--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/64.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/64.xlsx
@@ -426,13 +426,13 @@
         <v>-4.862885182453418</v>
       </c>
       <c r="E2">
-        <v>-10.64988728086578</v>
+        <v>-12.46403906003017</v>
       </c>
       <c r="F2">
-        <v>-2.772167280514374</v>
+        <v>-4.010523532185855</v>
       </c>
       <c r="G2">
-        <v>-3.913877629013967</v>
+        <v>-3.547289927252794</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-4.040144223885179</v>
       </c>
       <c r="E3">
-        <v>-12.81702464373867</v>
+        <v>-13.22052989000238</v>
       </c>
       <c r="F3">
-        <v>-3.218112244872265</v>
+        <v>-4.091617387450316</v>
       </c>
       <c r="G3">
-        <v>-4.209069298441963</v>
+        <v>-3.903071757151348</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.430697979483122</v>
       </c>
       <c r="E4">
-        <v>-13.05463401684343</v>
+        <v>-13.53799305724963</v>
       </c>
       <c r="F4">
-        <v>-2.636247928695628</v>
+        <v>-4.199046699184578</v>
       </c>
       <c r="G4">
-        <v>-2.5376523359991</v>
+        <v>-3.18592632541844</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-3.138181994378726</v>
       </c>
       <c r="E5">
-        <v>-12.65310985238166</v>
+        <v>-13.70522211124385</v>
       </c>
       <c r="F5">
-        <v>-2.491541255467985</v>
+        <v>-4.107886523241298</v>
       </c>
       <c r="G5">
-        <v>-2.514461091796241</v>
+        <v>-3.054903497368829</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.105206399864543</v>
       </c>
       <c r="E6">
-        <v>-13.17113159450487</v>
+        <v>-13.97593673181882</v>
       </c>
       <c r="F6">
-        <v>-3.752529332951352</v>
+        <v>-3.9431905162167</v>
       </c>
       <c r="G6">
-        <v>-2.862653487168429</v>
+        <v>-2.520596341585357</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.303017670651692</v>
       </c>
       <c r="E7">
-        <v>-14.98289527715748</v>
+        <v>-14.68194112492643</v>
       </c>
       <c r="F7">
-        <v>-3.14573115795045</v>
+        <v>-4.030251101883525</v>
       </c>
       <c r="G7">
-        <v>-3.058777842342041</v>
+        <v>-2.769857181421898</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.665937699174707</v>
       </c>
       <c r="E8">
-        <v>-14.90580752175734</v>
+        <v>-15.47601851738835</v>
       </c>
       <c r="F8">
-        <v>-2.948555693429487</v>
+        <v>-3.565181619297202</v>
       </c>
       <c r="G8">
-        <v>-2.649392204498749</v>
+        <v>-2.278436727036644</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.139063899173634</v>
       </c>
       <c r="E9">
-        <v>-14.39188915242305</v>
+        <v>-15.78895468429153</v>
       </c>
       <c r="F9">
-        <v>-2.8194596039076</v>
+        <v>-3.645462017772113</v>
       </c>
       <c r="G9">
-        <v>-2.643283062155544</v>
+        <v>-2.013790769324673</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.652439033110049</v>
       </c>
       <c r="E10">
-        <v>-15.29875945804466</v>
+        <v>-16.15907226471495</v>
       </c>
       <c r="F10">
-        <v>-2.487523673564408</v>
+        <v>-3.404234803137675</v>
       </c>
       <c r="G10">
-        <v>-2.431679602301221</v>
+        <v>-2.632015088500299</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.149990812215408</v>
       </c>
       <c r="E11">
-        <v>-16.70112033435229</v>
+        <v>-16.648362090893</v>
       </c>
       <c r="F11">
-        <v>-2.593265600899167</v>
+        <v>-3.440465108233917</v>
       </c>
       <c r="G11">
-        <v>-1.996050759828058</v>
+        <v>-2.489692957860349</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.577868081048219</v>
       </c>
       <c r="E12">
-        <v>-16.70068009395186</v>
+        <v>-17.43194431833707</v>
       </c>
       <c r="F12">
-        <v>-2.040585496690559</v>
+        <v>-2.997052463026384</v>
       </c>
       <c r="G12">
-        <v>-2.721166794797635</v>
+        <v>-2.071109666822565</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.902525291816201</v>
       </c>
       <c r="E13">
-        <v>-18.47547604260217</v>
+        <v>-17.92408324748396</v>
       </c>
       <c r="F13">
-        <v>-2.225571534879328</v>
+        <v>-2.98281282737226</v>
       </c>
       <c r="G13">
-        <v>-1.995304086875</v>
+        <v>-2.130799120409188</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-6.105151484219881</v>
       </c>
       <c r="E14">
-        <v>-19.64963456945577</v>
+        <v>-18.49942345910113</v>
       </c>
       <c r="F14">
-        <v>-1.874969173481452</v>
+        <v>-2.383247956532603</v>
       </c>
       <c r="G14">
-        <v>-2.105216434160869</v>
+        <v>-2.007287404548209</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.190059264437357</v>
       </c>
       <c r="E15">
-        <v>-18.90564490557128</v>
+        <v>-18.83968775652168</v>
       </c>
       <c r="F15">
-        <v>-1.319586106437509</v>
+        <v>-2.471203178994452</v>
       </c>
       <c r="G15">
-        <v>-1.614109269126549</v>
+        <v>-1.904598987545951</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.176040090600121</v>
       </c>
       <c r="E16">
-        <v>-17.48267994788118</v>
+        <v>-19.31160469972798</v>
       </c>
       <c r="F16">
-        <v>-1.157984051662367</v>
+        <v>-1.9894959371229</v>
       </c>
       <c r="G16">
-        <v>-0.7997736485002659</v>
+        <v>-1.638702483174836</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.09740417917857</v>
       </c>
       <c r="E17">
-        <v>-19.95342121181035</v>
+        <v>-20.20560005024262</v>
       </c>
       <c r="F17">
-        <v>-0.9260478058177283</v>
+        <v>-1.694745419491377</v>
       </c>
       <c r="G17">
-        <v>-1.677539919712237</v>
+        <v>-1.333806676101671</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.993822117679941</v>
       </c>
       <c r="E18">
-        <v>-21.36563350538048</v>
+        <v>-20.71964716912797</v>
       </c>
       <c r="F18">
-        <v>-0.6881903897778783</v>
+        <v>-1.600387745373291</v>
       </c>
       <c r="G18">
-        <v>-0.6501074933255145</v>
+        <v>-1.916913869782232</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.906742494950305</v>
       </c>
       <c r="E19">
-        <v>-21.08545786940754</v>
+        <v>-21.65769147895374</v>
       </c>
       <c r="F19">
-        <v>-0.4951501353316898</v>
+        <v>-1.335798084877698</v>
       </c>
       <c r="G19">
-        <v>-0.6404660135505332</v>
+        <v>-2.129966292884623</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.872730753979184</v>
       </c>
       <c r="E20">
-        <v>-21.62259269004762</v>
+        <v>-22.07983633764329</v>
       </c>
       <c r="F20">
-        <v>-0.2645077993702235</v>
+        <v>-0.8841953711586861</v>
       </c>
       <c r="G20">
-        <v>-1.296057920058764</v>
+        <v>-1.451224914086991</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.915228755436323</v>
       </c>
       <c r="E21">
-        <v>-22.99117965186175</v>
+        <v>-23.73246972838509</v>
       </c>
       <c r="F21">
-        <v>-0.08742438620416197</v>
+        <v>-0.6130889443052695</v>
       </c>
       <c r="G21">
-        <v>0.05628689218118936</v>
+        <v>-1.224855082825331</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-6.049588884963298</v>
       </c>
       <c r="E22">
-        <v>-22.62188440728064</v>
+        <v>-23.36507250137943</v>
       </c>
       <c r="F22">
-        <v>0.4633968615525637</v>
+        <v>-0.3607384121860392</v>
       </c>
       <c r="G22">
-        <v>-1.185375403118516</v>
+        <v>-1.683247007388411</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-6.273423423471462</v>
       </c>
       <c r="E23">
-        <v>-24.53631547388301</v>
+        <v>-23.69391546765671</v>
       </c>
       <c r="F23">
-        <v>0.5237194041918265</v>
+        <v>-0.1448559266076545</v>
       </c>
       <c r="G23">
-        <v>-2.136360006388259</v>
+        <v>-1.98123478427349</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-6.58301263240261</v>
       </c>
       <c r="E24">
-        <v>-23.36960365493482</v>
+        <v>-23.9975858200942</v>
       </c>
       <c r="F24">
-        <v>0.9545532903878493</v>
+        <v>0.02639826514490689</v>
       </c>
       <c r="G24">
-        <v>-1.860775028839523</v>
+        <v>-2.276836340602292</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-6.962131751620809</v>
       </c>
       <c r="E25">
-        <v>-23.6177871040726</v>
+        <v>-24.58620384831685</v>
       </c>
       <c r="F25">
-        <v>1.254203601206931</v>
+        <v>0.6327574054223254</v>
       </c>
       <c r="G25">
-        <v>-1.886261117537971</v>
+        <v>-2.561214305933897</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.401370987993834</v>
       </c>
       <c r="E26">
-        <v>-23.39711037353916</v>
+        <v>-24.80307208406542</v>
       </c>
       <c r="F26">
-        <v>1.251783111655951</v>
+        <v>0.9771561233406366</v>
       </c>
       <c r="G26">
-        <v>-2.324370167372691</v>
+        <v>-2.648507162082361</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.88018021314772</v>
       </c>
       <c r="E27">
-        <v>-24.7084910025651</v>
+        <v>-25.28004763866535</v>
       </c>
       <c r="F27">
-        <v>1.106677993707562</v>
+        <v>0.687350130736424</v>
       </c>
       <c r="G27">
-        <v>-2.841485570023682</v>
+        <v>-2.723529518652593</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.386341164747403</v>
       </c>
       <c r="E28">
-        <v>-25.22947398436292</v>
+        <v>-25.00434916450059</v>
       </c>
       <c r="F28">
-        <v>1.521753018432727</v>
+        <v>0.6091522479121507</v>
       </c>
       <c r="G28">
-        <v>-2.011433266958897</v>
+        <v>-2.869603289269972</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.895098843386185</v>
       </c>
       <c r="E29">
-        <v>-24.01430664888796</v>
+        <v>-25.04749687695423</v>
       </c>
       <c r="F29">
-        <v>1.301889399116488</v>
+        <v>0.8118918562777185</v>
       </c>
       <c r="G29">
-        <v>-2.297103550863104</v>
+        <v>-3.082825410770786</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.388890036363634</v>
       </c>
       <c r="E30">
-        <v>-24.41517045274908</v>
+        <v>-24.33392533281279</v>
       </c>
       <c r="F30">
-        <v>1.775901107816032</v>
+        <v>0.5892424373858646</v>
       </c>
       <c r="G30">
-        <v>-1.530338307431497</v>
+        <v>-3.267961141960402</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.840242393627848</v>
       </c>
       <c r="E31">
-        <v>-24.5728969592321</v>
+        <v>-24.44652719825154</v>
       </c>
       <c r="F31">
-        <v>1.008705324243659</v>
+        <v>0.7403242261454525</v>
       </c>
       <c r="G31">
-        <v>-2.389915521077182</v>
+        <v>-3.112517409005517</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-10.23165265929434</v>
       </c>
       <c r="E32">
-        <v>-24.1513127840714</v>
+        <v>-24.61471149085047</v>
       </c>
       <c r="F32">
-        <v>0.8151986989496941</v>
+        <v>0.5585274024574617</v>
       </c>
       <c r="G32">
-        <v>-2.645335107404159</v>
+        <v>-3.501531406804352</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-10.54272450380862</v>
       </c>
       <c r="E33">
-        <v>-23.94665498961782</v>
+        <v>-23.5808359829156</v>
       </c>
       <c r="F33">
-        <v>0.9501596296834007</v>
+        <v>0.6638460340493908</v>
       </c>
       <c r="G33">
-        <v>-2.911221168796909</v>
+        <v>-3.408152905014003</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-10.76138140504515</v>
       </c>
       <c r="E34">
-        <v>-22.85139501830199</v>
+        <v>-23.86392717323857</v>
       </c>
       <c r="F34">
-        <v>0.8328131034028228</v>
+        <v>0.6334416368970378</v>
       </c>
       <c r="G34">
-        <v>-1.986717347914828</v>
+        <v>-3.190051301872399</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-10.87661891727135</v>
       </c>
       <c r="E35">
-        <v>-21.75375525689703</v>
+        <v>-23.570062552739</v>
       </c>
       <c r="F35">
-        <v>0.9661090156569024</v>
+        <v>0.2023244490492575</v>
       </c>
       <c r="G35">
-        <v>-2.767959170104159</v>
+        <v>-3.444076750587722</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-10.87929556530912</v>
       </c>
       <c r="E36">
-        <v>-22.42161240398608</v>
+        <v>-22.9589714980377</v>
       </c>
       <c r="F36">
-        <v>1.129247691964237</v>
+        <v>0.5843012258281656</v>
       </c>
       <c r="G36">
-        <v>-2.179518225223953</v>
+        <v>-2.494697755241513</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-10.76621136634996</v>
       </c>
       <c r="E37">
-        <v>-22.07470296844581</v>
+        <v>-22.47556261909561</v>
       </c>
       <c r="F37">
-        <v>-0.1457281974828024</v>
+        <v>0.2479699780457187</v>
       </c>
       <c r="G37">
-        <v>-2.126875171288745</v>
+        <v>-3.03834876591658</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-10.53301538127436</v>
       </c>
       <c r="E38">
-        <v>-20.86996849981881</v>
+        <v>-21.72493197030272</v>
       </c>
       <c r="F38">
-        <v>0.3989490492473594</v>
+        <v>-0.2798972089794327</v>
       </c>
       <c r="G38">
-        <v>-1.395279268244024</v>
+        <v>-2.909080358232196</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-10.18752877044215</v>
       </c>
       <c r="E39">
-        <v>-21.09378505811383</v>
+        <v>-20.99076465120145</v>
       </c>
       <c r="F39">
-        <v>1.05580960823645</v>
+        <v>-0.4363385348351334</v>
       </c>
       <c r="G39">
-        <v>-1.787958751448782</v>
+        <v>-2.270980440484425</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.736374230626636</v>
       </c>
       <c r="E40">
-        <v>-20.37861868082365</v>
+        <v>-20.85738426950459</v>
       </c>
       <c r="F40">
-        <v>0.6436835714652509</v>
+        <v>-0.2544597027742655</v>
       </c>
       <c r="G40">
-        <v>-2.007326565717076</v>
+        <v>-2.065788969345876</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.200708555937526</v>
       </c>
       <c r="E41">
-        <v>-21.10899827119667</v>
+        <v>-20.14829819359396</v>
       </c>
       <c r="F41">
-        <v>-0.08860563812055407</v>
+        <v>-0.5296872574566096</v>
       </c>
       <c r="G41">
-        <v>-1.151226863866754</v>
+        <v>-2.079685962804372</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.599483189086561</v>
       </c>
       <c r="E42">
-        <v>-18.48091674943769</v>
+        <v>-20.44979641650856</v>
       </c>
       <c r="F42">
-        <v>0.2145718610996482</v>
+        <v>-0.6588844078016373</v>
       </c>
       <c r="G42">
-        <v>-1.155411887446309</v>
+        <v>-2.029872956005931</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-7.964833765436437</v>
       </c>
       <c r="E43">
-        <v>-19.66813712590788</v>
+        <v>-19.34205189195029</v>
       </c>
       <c r="F43">
-        <v>-0.2437331732754147</v>
+        <v>-0.8740437286373781</v>
       </c>
       <c r="G43">
-        <v>-0.3924191699488599</v>
+        <v>-1.840191918483186</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-7.324539492521042</v>
       </c>
       <c r="E44">
-        <v>-19.40641836106249</v>
+        <v>-19.36074549612335</v>
       </c>
       <c r="F44">
-        <v>0.1761960844301555</v>
+        <v>-1.282635121700831</v>
       </c>
       <c r="G44">
-        <v>-0.1961433915889631</v>
+        <v>-1.387410484046409</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.713758644583915</v>
       </c>
       <c r="E45">
-        <v>-18.36506707274292</v>
+        <v>-19.38528682184176</v>
       </c>
       <c r="F45">
-        <v>-0.4943698132382527</v>
+        <v>-1.195631693384799</v>
       </c>
       <c r="G45">
-        <v>-0.4958829780946795</v>
+        <v>-1.246748786966407</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.159578031448785</v>
       </c>
       <c r="E46">
-        <v>-18.40904542746154</v>
+        <v>-18.77511778005457</v>
       </c>
       <c r="F46">
-        <v>-0.1436647342824288</v>
+        <v>-0.9712600986625253</v>
       </c>
       <c r="G46">
-        <v>-0.3634842876455514</v>
+        <v>-1.365320974060999</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.688788955932282</v>
       </c>
       <c r="E47">
-        <v>-16.59418344916061</v>
+        <v>-17.97858168648836</v>
       </c>
       <c r="F47">
-        <v>-0.1556835169296468</v>
+        <v>-1.148068493850857</v>
       </c>
       <c r="G47">
-        <v>0.1145587114548379</v>
+        <v>-1.557698910746364</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.317914253574235</v>
       </c>
       <c r="E48">
-        <v>-17.12981065408977</v>
+        <v>-18.03111565653611</v>
       </c>
       <c r="F48">
-        <v>-0.6580858616253386</v>
+        <v>-1.298385699497661</v>
       </c>
       <c r="G48">
-        <v>-0.3507229680841897</v>
+        <v>-1.508233132978541</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.05887145957169</v>
       </c>
       <c r="E49">
-        <v>-17.17024216633698</v>
+        <v>-17.45703386795036</v>
       </c>
       <c r="F49">
-        <v>-0.3232274510850692</v>
+        <v>-1.379554107828374</v>
       </c>
       <c r="G49">
-        <v>-0.7822529415493047</v>
+        <v>-0.9427328008204472</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.915110995670944</v>
       </c>
       <c r="E50">
-        <v>-16.25136492677529</v>
+        <v>-17.00844551275563</v>
       </c>
       <c r="F50">
-        <v>-1.007413365590307</v>
+        <v>-1.668424873634826</v>
       </c>
       <c r="G50">
-        <v>-1.000485081920464</v>
+        <v>-1.177329088288705</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.883717699163062</v>
       </c>
       <c r="E51">
-        <v>-16.33665527454196</v>
+        <v>-16.8504656603818</v>
       </c>
       <c r="F51">
-        <v>-0.275396688880023</v>
+        <v>-1.501276070730539</v>
       </c>
       <c r="G51">
-        <v>-0.6990406791967509</v>
+        <v>-1.21254020058905</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.955332115248134</v>
       </c>
       <c r="E52">
-        <v>-15.35211991714606</v>
+        <v>-16.63928317093692</v>
       </c>
       <c r="F52">
-        <v>-0.4503702502711542</v>
+        <v>-1.795860086514099</v>
       </c>
       <c r="G52">
-        <v>0.1429505588831949</v>
+        <v>-0.7243335727954564</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.114648967382629</v>
       </c>
       <c r="E53">
-        <v>-15.4685012048904</v>
+        <v>-15.67980829067503</v>
       </c>
       <c r="F53">
-        <v>-0.4738528094057146</v>
+        <v>-1.712923942145812</v>
       </c>
       <c r="G53">
-        <v>-0.5281700564529774</v>
+        <v>-1.121049267138076</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.34316204562585</v>
       </c>
       <c r="E54">
-        <v>-15.59167714636217</v>
+        <v>-16.10375564307956</v>
       </c>
       <c r="F54">
-        <v>-0.4516194283145758</v>
+        <v>-1.948882740098446</v>
       </c>
       <c r="G54">
-        <v>-0.6512875498806978</v>
+        <v>-1.531601907813595</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.622152188509104</v>
       </c>
       <c r="E55">
-        <v>-14.9695676220161</v>
+        <v>-15.47928709470099</v>
       </c>
       <c r="F55">
-        <v>-0.9640127122554324</v>
+        <v>-1.943571248311695</v>
       </c>
       <c r="G55">
-        <v>-1.002095911333181</v>
+        <v>-1.238104611625231</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.934660472845911</v>
       </c>
       <c r="E56">
-        <v>-14.19595310175162</v>
+        <v>-15.42923674502548</v>
       </c>
       <c r="F56">
-        <v>-0.8162526767810706</v>
+        <v>-2.285568529129291</v>
       </c>
       <c r="G56">
-        <v>-0.205842307744949</v>
+        <v>-1.296060530803355</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.268479976281612</v>
       </c>
       <c r="E57">
-        <v>-15.01057227742614</v>
+        <v>-14.73186272505087</v>
       </c>
       <c r="F57">
-        <v>-1.001207237008533</v>
+        <v>-2.212326768475967</v>
       </c>
       <c r="G57">
-        <v>-1.513467675883723</v>
+        <v>-1.85748549065472</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.616610637494652</v>
       </c>
       <c r="E58">
-        <v>-13.45534830509687</v>
+        <v>-14.64472835145596</v>
       </c>
       <c r="F58">
-        <v>-1.176755685377207</v>
+        <v>-1.92315282020009</v>
       </c>
       <c r="G58">
-        <v>-0.9030782012260276</v>
+        <v>-1.348285865603985</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.974659604257053</v>
       </c>
       <c r="E59">
-        <v>-14.27943264938067</v>
+        <v>-13.90386190248775</v>
       </c>
       <c r="F59">
-        <v>-1.302998049196449</v>
+        <v>-2.461493056298836</v>
       </c>
       <c r="G59">
-        <v>-1.626084754565985</v>
+        <v>-1.295710691028146</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.340480883965887</v>
       </c>
       <c r="E60">
-        <v>-13.73216399310801</v>
+        <v>-14.35140364842862</v>
       </c>
       <c r="F60">
-        <v>-1.761841522383331</v>
+        <v>-2.240689239980419</v>
       </c>
       <c r="G60">
-        <v>-1.696909033833707</v>
+        <v>-1.468064216699671</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.708774730401724</v>
       </c>
       <c r="E61">
-        <v>-14.19276343545415</v>
+        <v>-14.96497417029084</v>
       </c>
       <c r="F61">
-        <v>-1.695161259927582</v>
+        <v>-2.295529647147955</v>
       </c>
       <c r="G61">
-        <v>-1.7586635863919</v>
+        <v>-2.172184643667516</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.077844341424308</v>
       </c>
       <c r="E62">
-        <v>-13.82826514995322</v>
+        <v>-13.69265449377492</v>
       </c>
       <c r="F62">
-        <v>-1.852095464387949</v>
+        <v>-2.641601667219921</v>
       </c>
       <c r="G62">
-        <v>-1.463766931102699</v>
+        <v>-2.130420562443477</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.440562534661296</v>
       </c>
       <c r="E63">
-        <v>-12.67206510886818</v>
+        <v>-13.4896455242173</v>
       </c>
       <c r="F63">
-        <v>-1.745067082476641</v>
+        <v>-2.843463206138522</v>
       </c>
       <c r="G63">
-        <v>-2.306275096611685</v>
+        <v>-2.220580016152983</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.796381894849135</v>
       </c>
       <c r="E64">
-        <v>-12.64613661056727</v>
+        <v>-13.5077286063256</v>
       </c>
       <c r="F64">
-        <v>-1.590072914473632</v>
+        <v>-2.721136535032313</v>
       </c>
       <c r="G64">
-        <v>-2.641066539997689</v>
+        <v>-2.986076437713309</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.136721309692318</v>
       </c>
       <c r="E65">
-        <v>-13.58635304991593</v>
+        <v>-13.05043927340536</v>
       </c>
       <c r="F65">
-        <v>-1.414349680582967</v>
+        <v>-2.848735764657341</v>
       </c>
       <c r="G65">
-        <v>-2.36041149645301</v>
+        <v>-2.461966850302726</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.461587741674249</v>
       </c>
       <c r="E66">
-        <v>-12.77001029154161</v>
+        <v>-14.30570171101021</v>
       </c>
       <c r="F66">
-        <v>-1.885632747057689</v>
+        <v>-2.713638981669575</v>
       </c>
       <c r="G66">
-        <v>-2.160660817042342</v>
+        <v>-3.108225344897726</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.761480578662288</v>
       </c>
       <c r="E67">
-        <v>-13.34092317988651</v>
+        <v>-13.55289062627179</v>
       </c>
       <c r="F67">
-        <v>-2.514104326785438</v>
+        <v>-2.622312303878332</v>
       </c>
       <c r="G67">
-        <v>-1.786371418737386</v>
+        <v>-2.688678689105822</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-10.03576554871986</v>
       </c>
       <c r="E68">
-        <v>-14.46326208904023</v>
+        <v>-12.78142746947356</v>
       </c>
       <c r="F68">
-        <v>-1.720983956975051</v>
+        <v>-3.081085365835976</v>
       </c>
       <c r="G68">
-        <v>-3.237984572565239</v>
+        <v>-3.604799409105838</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-10.27365570639185</v>
       </c>
       <c r="E69">
-        <v>-10.58091490039436</v>
+        <v>-13.51831514199259</v>
       </c>
       <c r="F69">
-        <v>-2.204882230627008</v>
+        <v>-3.024879809188627</v>
       </c>
       <c r="G69">
-        <v>-1.673065103483069</v>
+        <v>-3.087665731242709</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-10.47145653735808</v>
       </c>
       <c r="E70">
-        <v>-12.67295804930301</v>
+        <v>-13.35994488775423</v>
       </c>
       <c r="F70">
-        <v>-2.03793140753199</v>
+        <v>-3.098891123159152</v>
       </c>
       <c r="G70">
-        <v>-3.20639717375736</v>
+        <v>-3.610347241361954</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.61722034170398</v>
       </c>
       <c r="E71">
-        <v>-12.45033761586956</v>
+        <v>-12.84751752128556</v>
       </c>
       <c r="F71">
-        <v>-2.415768832399109</v>
+        <v>-3.408694733234348</v>
       </c>
       <c r="G71">
-        <v>-2.244925209465114</v>
+        <v>-3.35585185862023</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.70415423405386</v>
       </c>
       <c r="E72">
-        <v>-12.84227616859362</v>
+        <v>-13.17698762247288</v>
       </c>
       <c r="F72">
-        <v>-2.222668935499919</v>
+        <v>-3.183440927228092</v>
       </c>
       <c r="G72">
-        <v>-1.50593306699377</v>
+        <v>-3.623643763564494</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.72275734997062</v>
       </c>
       <c r="E73">
-        <v>-13.70212796880685</v>
+        <v>-13.26006430860343</v>
       </c>
       <c r="F73">
-        <v>-2.759310190055523</v>
+        <v>-3.299290593611811</v>
       </c>
       <c r="G73">
-        <v>-2.797518020364743</v>
+        <v>-3.252615185253838</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.66687678804458</v>
       </c>
       <c r="E74">
-        <v>-13.36177645394848</v>
+        <v>-13.8928475860543</v>
       </c>
       <c r="F74">
-        <v>-2.5918548912122</v>
+        <v>-3.441218094203061</v>
       </c>
       <c r="G74">
-        <v>-2.563141035442139</v>
+        <v>-3.921641983427937</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.53601508369162</v>
       </c>
       <c r="E75">
-        <v>-12.00185724416927</v>
+        <v>-13.37943590850165</v>
       </c>
       <c r="F75">
-        <v>-2.816686229843028</v>
+        <v>-3.646547179069781</v>
       </c>
       <c r="G75">
-        <v>-2.329570770598189</v>
+        <v>-2.929235306475591</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.33117795050688</v>
       </c>
       <c r="E76">
-        <v>-13.46553197926534</v>
+        <v>-14.03648224651217</v>
       </c>
       <c r="F76">
-        <v>-2.512401203405283</v>
+        <v>-3.467479825974014</v>
       </c>
       <c r="G76">
-        <v>-2.202800845487501</v>
+        <v>-3.18822378065862</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.06397372997941</v>
       </c>
       <c r="E77">
-        <v>-13.01636217448514</v>
+        <v>-15.051331893368</v>
       </c>
       <c r="F77">
-        <v>-3.055492954926486</v>
+        <v>-3.62448775513323</v>
       </c>
       <c r="G77">
-        <v>-2.50690820769415</v>
+        <v>-3.134314515596722</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.742619712531567</v>
       </c>
       <c r="E78">
-        <v>-14.06719109104796</v>
+        <v>-14.97601340599224</v>
       </c>
       <c r="F78">
-        <v>-2.674758729251777</v>
+        <v>-3.585173438196365</v>
       </c>
       <c r="G78">
-        <v>-1.812538911774114</v>
+        <v>-2.871433421228343</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.38547459484805</v>
       </c>
       <c r="E79">
-        <v>-14.84693990443922</v>
+        <v>-15.27379035155979</v>
       </c>
       <c r="F79">
-        <v>-2.452595562025366</v>
+        <v>-3.434631744983403</v>
       </c>
       <c r="G79">
-        <v>-1.344327976803857</v>
+        <v>-2.76310840665387</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.002526239552292</v>
       </c>
       <c r="E80">
-        <v>-15.38223069925107</v>
+        <v>-15.96817405938053</v>
       </c>
       <c r="F80">
-        <v>-2.938489372750667</v>
+        <v>-3.696925999405838</v>
       </c>
       <c r="G80">
-        <v>-1.279503188606514</v>
+        <v>-2.936305202828326</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.612758133319854</v>
       </c>
       <c r="E81">
-        <v>-17.92394203829891</v>
+        <v>-16.90955755111147</v>
       </c>
       <c r="F81">
-        <v>-2.899136950913273</v>
+        <v>-3.835271639347384</v>
       </c>
       <c r="G81">
-        <v>-1.136178532043577</v>
+        <v>-2.231944587358099</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.225460433002754</v>
       </c>
       <c r="E82">
-        <v>-17.6595942906849</v>
+        <v>-18.0828023714736</v>
       </c>
       <c r="F82">
-        <v>-3.010853063957023</v>
+        <v>-3.614127364026416</v>
       </c>
       <c r="G82">
-        <v>-1.227444941459715</v>
+        <v>-2.225462108538364</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.858090791293413</v>
       </c>
       <c r="E83">
-        <v>-17.52767583937437</v>
+        <v>-18.97688078621474</v>
       </c>
       <c r="F83">
-        <v>-3.316986178070414</v>
+        <v>-3.669478045514077</v>
       </c>
       <c r="G83">
-        <v>-0.8420102744952966</v>
+        <v>-1.7270526908827</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.517957143048808</v>
       </c>
       <c r="E84">
-        <v>-19.30593556626958</v>
+        <v>-19.20306467496491</v>
       </c>
       <c r="F84">
-        <v>-3.640189459253294</v>
+        <v>-3.484003270557656</v>
       </c>
       <c r="G84">
-        <v>-0.8703133566075558</v>
+        <v>-1.792047177478466</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.219093950240801</v>
       </c>
       <c r="E85">
-        <v>-19.76268082850628</v>
+        <v>-21.06699269185736</v>
       </c>
       <c r="F85">
-        <v>-3.085033364877719</v>
+        <v>-3.834720775024522</v>
       </c>
       <c r="G85">
-        <v>-0.7817830075229043</v>
+        <v>-1.943517357165676</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.967002234615669</v>
       </c>
       <c r="E86">
-        <v>-21.94659716513147</v>
+        <v>-22.41418230892597</v>
       </c>
       <c r="F86">
-        <v>-3.768664273223081</v>
+        <v>-3.629926815500011</v>
       </c>
       <c r="G86">
-        <v>-1.103909728897417</v>
+        <v>-1.623087619775387</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.773572663642764</v>
       </c>
       <c r="E87">
-        <v>-22.69337363381491</v>
+        <v>-23.48266652683063</v>
       </c>
       <c r="F87">
-        <v>-3.207370804760164</v>
+        <v>-3.380722422776614</v>
       </c>
       <c r="G87">
-        <v>-0.6777448355670398</v>
+        <v>-1.52244341578797</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.643526760582816</v>
       </c>
       <c r="E88">
-        <v>-24.20786290947026</v>
+        <v>-24.11943273394202</v>
       </c>
       <c r="F88">
-        <v>-3.248054413013856</v>
+        <v>-3.583047019073379</v>
       </c>
       <c r="G88">
-        <v>-0.4970369272039515</v>
+        <v>-1.66584378394405</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.586559154844213</v>
       </c>
       <c r="E89">
-        <v>-26.16101021204268</v>
+        <v>-26.02573181277037</v>
       </c>
       <c r="F89">
-        <v>-3.036958234288847</v>
+        <v>-3.499069616879773</v>
       </c>
       <c r="G89">
-        <v>0.1406243854525129</v>
+        <v>-1.518435922840611</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.605175018402272</v>
       </c>
       <c r="E90">
-        <v>-29.04124565296598</v>
+        <v>-27.24173809693294</v>
       </c>
       <c r="F90">
-        <v>-3.123371036646683</v>
+        <v>-3.55145722816762</v>
       </c>
       <c r="G90">
-        <v>-0.8255860802726029</v>
+        <v>-1.386509777162475</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.706228800931021</v>
       </c>
       <c r="E91">
-        <v>-30.53765184651303</v>
+        <v>-30.10425801495018</v>
       </c>
       <c r="F91">
-        <v>-3.18786689426125</v>
+        <v>-3.442266807335006</v>
       </c>
       <c r="G91">
-        <v>-0.6906706320376417</v>
+        <v>-1.939945858565033</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.888096193288722</v>
       </c>
       <c r="E92">
-        <v>-30.35615235840669</v>
+        <v>-31.03866826486673</v>
       </c>
       <c r="F92">
-        <v>-2.790671351558109</v>
+        <v>-3.214094662968688</v>
       </c>
       <c r="G92">
-        <v>-0.6541959193551979</v>
+        <v>-1.795655226503384</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.153112550336469</v>
       </c>
       <c r="E93">
-        <v>-31.95393636378714</v>
+        <v>-32.92003146290081</v>
       </c>
       <c r="F93">
-        <v>-2.802108620288562</v>
+        <v>-3.188208181631203</v>
       </c>
       <c r="G93">
-        <v>-0.5158551742166961</v>
+        <v>-2.220138800317085</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-7.49361358212562</v>
       </c>
       <c r="E94">
-        <v>-33.49523461854427</v>
+        <v>-34.74310226338526</v>
       </c>
       <c r="F94">
-        <v>-3.016082547370897</v>
+        <v>-3.311389727897101</v>
       </c>
       <c r="G94">
-        <v>-0.6267439399796418</v>
+        <v>-2.135720373963436</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-7.904168887534055</v>
       </c>
       <c r="E95">
-        <v>-36.24697177768303</v>
+        <v>-37.52637267950779</v>
       </c>
       <c r="F95">
-        <v>-2.712842092228081</v>
+        <v>-3.086564187838092</v>
       </c>
       <c r="G95">
-        <v>-1.84601648966596</v>
+        <v>-2.886677558895853</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.374906306615475</v>
       </c>
       <c r="E96">
-        <v>-39.31873878866778</v>
+        <v>-38.63068042169476</v>
       </c>
       <c r="F96">
-        <v>-2.937281613077385</v>
+        <v>-3.137879063339313</v>
       </c>
       <c r="G96">
-        <v>-2.046200552678753</v>
+        <v>-2.866031790669329</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.888791047686885</v>
       </c>
       <c r="E97">
-        <v>-41.8921038278278</v>
+        <v>-41.71066456128568</v>
       </c>
       <c r="F97">
-        <v>-3.087841530373209</v>
+        <v>-3.05023613538832</v>
       </c>
       <c r="G97">
-        <v>-1.892618280617332</v>
+        <v>-3.442523357556009</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.440611407029548</v>
       </c>
       <c r="E98">
-        <v>-43.39618515590313</v>
+        <v>-43.63849388762194</v>
       </c>
       <c r="F98">
-        <v>-2.910986746610321</v>
+        <v>-2.689201314919587</v>
       </c>
       <c r="G98">
-        <v>-2.76036451408861</v>
+        <v>-3.886527468677464</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.00034941404304</v>
       </c>
       <c r="E99">
-        <v>-45.36313773291928</v>
+        <v>-45.08868106894064</v>
       </c>
       <c r="F99">
-        <v>-3.142585018554617</v>
+        <v>-2.677491513313613</v>
       </c>
       <c r="G99">
-        <v>-2.789899867647875</v>
+        <v>-3.708435526394671</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.57831807265196</v>
       </c>
       <c r="E100">
-        <v>-48.08829433957914</v>
+        <v>-47.61534324675296</v>
       </c>
       <c r="F100">
-        <v>-2.619565437570649</v>
+        <v>-2.829059553738644</v>
       </c>
       <c r="G100">
-        <v>-3.159343723991725</v>
+        <v>-4.333466056719329</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.12063517989246</v>
       </c>
       <c r="E101">
-        <v>-49.31427040752696</v>
+        <v>-49.88031261729068</v>
       </c>
       <c r="F101">
-        <v>-2.706839742027396</v>
+        <v>-2.626247877409032</v>
       </c>
       <c r="G101">
-        <v>-3.399527004884965</v>
+        <v>-4.887233702684959</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.68155502968118</v>
       </c>
       <c r="E102">
-        <v>-51.86545729821241</v>
+        <v>-51.39226428082656</v>
       </c>
       <c r="F102">
-        <v>-2.787012452739944</v>
+        <v>-2.936324848727152</v>
       </c>
       <c r="G102">
-        <v>-4.489160421154962</v>
+        <v>-5.128999094800414</v>
       </c>
     </row>
   </sheetData>
